--- a/main/ig/StructureDefinition-FRLMResultData.xlsx
+++ b/main/ig/StructureDefinition-FRLMResultData.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:19:44+00:00</t>
+    <t>2026-09-14T09:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMResultData.xlsx
+++ b/main/ig/StructureDefinition-FRLMResultData.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Logical model - FR LM Compte rendu de biologie de 1er niveau</t>
+    <t>Logical model - FR LM Result Data</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:04:12+00:00</t>
+    <t>2026-09-23T09:36:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -368,14 +368,14 @@
     <t>FRLMSection.entry</t>
   </si>
   <si>
-    <t>FRLMResultData.entry.resultatsExamensBiologieMedicale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMResultatsExamensBiologieMedicale
+    <t>FRLMResultData.entry.laboratoryTestResults</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMLaboratoryObservation
 </t>
   </si>
   <si>
-    <t>Entrée Résultats d'examens de biologie médicale</t>
+    <t>Résultats d'examens de biologie médicale</t>
   </si>
 </sst>
 </file>
@@ -680,8 +680,8 @@
   <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.30078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.38671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.38671875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -690,7 +690,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="86.52734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="76.87109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -711,7 +711,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.30078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.1875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1940,10 +1940,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -2015,10 +2015,10 @@
         <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>

--- a/main/ig/StructureDefinition-FRLMResultData.xlsx
+++ b/main/ig/StructureDefinition-FRLMResultData.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:36:17+00:00</t>
+    <t>2026-09-28T10:07:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMResultData.xlsx
+++ b/main/ig/StructureDefinition-FRLMResultData.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:07:47+00:00</t>
+    <t>2026-09-30T20:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,7 +362,7 @@
     <t>FRLMResultData.entry</t>
   </si>
   <si>
-    <t>Entrées</t>
+    <t>Modèles logiques contenus dans la section</t>
   </si>
   <si>
     <t>FRLMSection.entry</t>

--- a/main/ig/StructureDefinition-FRLMResultData.xlsx
+++ b/main/ig/StructureDefinition-FRLMResultData.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:10:21+00:00</t>
+    <t>2026-10-08T12:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
